--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487514_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487514_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3417</v>
+        <v>4.8956</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9261</v>
+        <v>3.774</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4156</v>
+        <v>1.1216</v>
       </c>
       <c r="G2" t="n">
         <v>1.1434</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1189</v>
+        <v>0.6727</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4815</v>
+        <v>0.3293</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6374</v>
+        <v>0.3433</v>
       </c>
       <c r="V2" t="n">
         <v>2.1003</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1389</v>
+        <v>3.823</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6012</v>
+        <v>1.4724</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5377</v>
+        <v>2.3506</v>
       </c>
       <c r="G3" t="n">
         <v>2.6462</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0423</v>
+        <v>-0.2736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2358</v>
+        <v>0.107</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1935</v>
+        <v>-0.3807</v>
       </c>
       <c r="V3" t="n">
         <v>0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6883</v>
+        <v>2.7805</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6627</v>
+        <v>3.5143</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9744</v>
+        <v>-0.7338</v>
       </c>
       <c r="G4" t="n">
         <v>2.4588</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1657</v>
+        <v>-1.0735</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0998</v>
+        <v>-0.2482</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0659</v>
+        <v>-0.8253</v>
       </c>
       <c r="V4" t="n">
         <v>2.7662</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4404</v>
+        <v>1.3766</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7961</v>
+        <v>1.4458</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3558</v>
+        <v>-0.0692</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9092</v>
+        <v>3.1103</v>
       </c>
       <c r="H5" t="n">
-        <v>1.702</v>
+        <v>-1.8459</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7927</v>
+        <v>4.9562</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3019</v>
+        <v>4.2833</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4936</v>
+        <v>-1.3084</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8083</v>
+        <v>5.5917</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3927</v>
+        <v>-1.173</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2083</v>
+        <v>-0.5375</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.601</v>
+        <v>-0.6355</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-4.8962</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6118</v>
+        <v>-1.425</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4734</v>
+        <v>-0.6499</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1384</v>
+        <v>-0.7752</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1152</v>
+        <v>2.4332</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1152</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1019</v>
+        <v>0.4967</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4918</v>
+        <v>1.3603</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3899</v>
+        <v>-0.8636</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1103</v>
+        <v>0.9092</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8459</v>
+        <v>1.702</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9562</v>
+        <v>-0.7927</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2833</v>
+        <v>2.3019</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3084</v>
+        <v>1.4936</v>
       </c>
       <c r="L6" t="n">
-        <v>5.5917</v>
+        <v>0.8083</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.173</v>
+        <v>-1.3927</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5375</v>
+        <v>0.2083</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6355</v>
+        <v>-1.601</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7419</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.6998</v>
+        <v>-0.3319</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6039</v>
+        <v>0.0376</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0959</v>
+        <v>-0.3695</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4332</v>
+        <v>0.1152</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0405</v>
+        <v>0.1006</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6933</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6529</v>
+        <v>0.84</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0356</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7502</v>
+        <v>-0.6092</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5445</v>
+        <v>-0.5905</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2058</v>
+        <v>-0.0187</v>
       </c>
       <c r="V7" t="n">
         <v>2.1578</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4658</v>
+        <v>-2.6644</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8575</v>
+        <v>-2.2699</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6083</v>
+        <v>-0.3944</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8435</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7179</v>
+        <v>0.0835</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2088</v>
+        <v>0.3788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5091</v>
+        <v>-0.2952</v>
       </c>
       <c r="V8" t="n">
         <v>-1.492</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8045</v>
+        <v>-4.9231</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7007</v>
+        <v>-1.846</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1038</v>
+        <v>-3.0771</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2694</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0063</v>
+        <v>-0.1248</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2664</v>
+        <v>0.1212</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2727</v>
+        <v>-0.246</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5495</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.400399999999999</v>
+        <v>5.8855</v>
       </c>
       <c r="E10" t="n">
-        <v>5.2264</v>
+        <v>6.711499999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8260000000000001</v>
+        <v>-0.8259000000000003</v>
       </c>
       <c r="G10" t="n">
         <v>4.119400000000001</v>
@@ -1210,16 +1210,16 @@
         <v>9.588699999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>2.343500000000001</v>
+        <v>2.3435</v>
       </c>
       <c r="L10" t="n">
-        <v>7.245</v>
+        <v>7.245000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>-5.4693</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2968999999999999</v>
+        <v>-0.2968999999999998</v>
       </c>
       <c r="O10" t="n">
         <v>-5.1723</v>
@@ -1234,16 +1234,16 @@
         <v>12.7301</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.5669</v>
+        <v>-3.0818</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9999</v>
+        <v>-0.5147000000000002</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.5671</v>
+        <v>-2.5673</v>
       </c>
       <c r="V10" t="n">
-        <v>6.806599999999999</v>
+        <v>6.8066</v>
       </c>
       <c r="W10" t="n">
         <v>12.3264</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.4417</v>
+        <v>6.9698</v>
       </c>
       <c r="E11" t="n">
-        <v>8.165100000000001</v>
+        <v>7.9604</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7234</v>
+        <v>-0.9907</v>
       </c>
       <c r="G11" t="n">
         <v>3.7557</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5281</v>
+        <v>0.0562</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0612</v>
+        <v>-0.2658</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5893</v>
+        <v>0.322</v>
       </c>
       <c r="V11" t="n">
         <v>2.7662</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.0617</v>
+        <v>1.3525</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3677</v>
+        <v>0.1397</v>
       </c>
       <c r="F12" t="n">
-        <v>1.694</v>
+        <v>1.2128</v>
       </c>
       <c r="G12" t="n">
         <v>0.07729999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4598</v>
+        <v>1.7506</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4849</v>
+        <v>1.2568</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9749</v>
+        <v>0.4937</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0629</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3837</v>
+        <v>0.5754</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8181</v>
+        <v>1.1059</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4343</v>
+        <v>-0.5305</v>
       </c>
       <c r="G13" t="n">
-        <v>0.534</v>
+        <v>0.4838</v>
       </c>
       <c r="H13" t="n">
-        <v>1.267</v>
+        <v>-0.0108</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.733</v>
+        <v>0.4946</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9882</v>
+        <v>1.6119</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3982</v>
+        <v>0.461</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5899</v>
+        <v>1.1509</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4542</v>
+        <v>-1.1281</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1312</v>
+        <v>-0.4718</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3229</v>
+        <v>-0.6563</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5875</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
-        <v>2.546</v>
+        <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4201</v>
+        <v>-0.4158</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4543</v>
+        <v>0.2358</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0342</v>
+        <v>-0.6516</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1578</v>
+        <v>1.0949</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6659</v>
+        <v>1.2166</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.492</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1543</v>
+        <v>0.181</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1543</v>
+        <v>0.181</v>
       </c>
       <c r="G14" t="n">
         <v>0.1364</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0503</v>
+        <v>0.1114</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4465</v>
+        <v>0.3854</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3962</v>
+        <v>-0.274</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4121</v>
+        <v>0.534</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5727</v>
+        <v>1.267</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8394</v>
+        <v>-0.733</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4746</v>
+        <v>1.9882</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3727</v>
+        <v>1.3982</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.102</v>
+        <v>0.5899</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9375</v>
+        <v>-1.4542</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2</v>
+        <v>-0.1312</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7375</v>
+        <v>-1.3229</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9965000000000001</v>
+        <v>1.1477</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3129</v>
+        <v>1.0216</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6837</v>
+        <v>0.1262</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4866</v>
+        <v>-2.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6083</v>
+        <v>-0.6659</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1217</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1547</v>
+        <v>-0.2078</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6965</v>
+        <v>0.2419</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.4497</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4838</v>
+        <v>-2.4121</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0108</v>
+        <v>-0.5727</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4946</v>
+        <v>-1.8394</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6119</v>
+        <v>-0.4746</v>
       </c>
       <c r="K16" t="n">
-        <v>0.461</v>
+        <v>-0.3727</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1509</v>
+        <v>-0.102</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1281</v>
+        <v>-1.9375</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4718</v>
+        <v>-0.2</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6563</v>
+        <v>-1.7375</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1459</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1735</v>
+        <v>0.1082</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9724</v>
+        <v>0.6302</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0949</v>
+        <v>0.4866</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X16" t="n">
         <v>-0.1217</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.1592</v>
+        <v>-4.3194</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9505</v>
+        <v>-2.1513</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2087</v>
+        <v>-2.1681</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0134</v>
+        <v>-0.5087</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4223</v>
+        <v>-1.4838</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4357</v>
+        <v>0.9752</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.429</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3504</v>
+        <v>-0.6058</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7794</v>
+        <v>1.3482</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5844</v>
+        <v>-1.2511</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.8781</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6563</v>
+        <v>-0.373</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9377</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>2.9377</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3468</v>
+        <v>-0.0197</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8828</v>
+        <v>-0.2117</v>
       </c>
       <c r="U17" t="n">
-        <v>0.464</v>
+        <v>0.192</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.5549</v>
+        <v>-4.7703</v>
       </c>
       <c r="W17" t="n">
-        <v>1.492</v>
+        <v>-0.7235</v>
       </c>
       <c r="X17" t="n">
         <v>-4.0468</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.801</v>
+        <v>-4.9545</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6864</v>
+        <v>-2.7458</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1147</v>
+        <v>-2.2087</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5087</v>
+        <v>-1.0134</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4838</v>
+        <v>0.4223</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9752</v>
+        <v>-1.4357</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7423999999999999</v>
+        <v>-0.429</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6058</v>
+        <v>0.3504</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3482</v>
+        <v>-0.7794</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2511</v>
+        <v>-0.5844</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8781</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.373</v>
+        <v>-0.6563</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9377</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5013</v>
+        <v>1.5515</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.7468</v>
+        <v>1.0875</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2455</v>
+        <v>0.464</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.7703</v>
+        <v>-2.5549</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7235</v>
+        <v>1.492</v>
       </c>
       <c r="X18" t="n">
         <v>-4.0468</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.3411</v>
+        <v>-5.8783</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.9561</v>
+        <v>-4.5468</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.385</v>
+        <v>-1.3315</v>
       </c>
       <c r="G19" t="n">
         <v>-5.3173</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3947</v>
+        <v>-0.9319</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2474</v>
+        <v>-0.8381</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1473</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.364300000000001</v>
+        <v>-6.169900000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9008999999999991</v>
+        <v>0.3893999999999993</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.2653</v>
+        <v>-6.559399999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2643</v>
@@ -1990,13 +1990,13 @@
         <v>5.2056</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1947000000000001</v>
+        <v>0.1946999999999997</v>
       </c>
       <c r="L20" t="n">
         <v>5.0107</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.469999999999999</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>-2.4821</v>
@@ -2005,7 +2005,7 @@
         <v>-6.9877</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9791</v>
+        <v>0.9791000000000001</v>
       </c>
       <c r="Q20" t="n">
         <v>-12.7301</v>
@@ -2014,13 +2014,13 @@
         <v>13.7092</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7272</v>
+        <v>3.921600000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>2.906000000000001</v>
+        <v>2.3943</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8213</v>
+        <v>1.5273</v>
       </c>
       <c r="V20" t="n">
         <v>-6.8065</v>
